--- a/data/Rickenbach (LU)/investment_decision/Pfeffikon LU_district_investment_decision.xlsx
+++ b/data/Rickenbach (LU)/investment_decision/Pfeffikon LU_district_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,13 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,27 +470,27 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
@@ -528,7 +527,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
@@ -565,7 +564,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
@@ -602,7 +601,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
@@ -639,7 +638,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
@@ -676,11 +675,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1460725368385857</v>
+        <v>0.164195226</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -694,30 +693,30 @@
         <v>4.353722540108308</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1457282147454773</v>
+        <v>0.164195226</v>
       </c>
       <c r="G7" t="n">
         <v>4.353722540108308</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1471041155351684</v>
+        <v>0.1701122353411765</v>
       </c>
       <c r="I7" t="n">
         <v>1.215090118284824</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1471041155351684</v>
+        <v>0.1701122353411765</v>
       </c>
       <c r="K7" t="n">
         <v>1.215090118284824</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1464370918844717</v>
+        <v>0.1701122353411765</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -731,30 +730,30 @@
         <v>4.353722540108308</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1457282147454773</v>
+        <v>0.1701122353411765</v>
       </c>
       <c r="G8" t="n">
         <v>4.353722540108308</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1489844984406758</v>
+        <v>0.1792580826117647</v>
       </c>
       <c r="I8" t="n">
         <v>1.823077759278831</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1489844984406758</v>
+        <v>0.1792580826117647</v>
       </c>
       <c r="K8" t="n">
         <v>1.823077759278831</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1523982481882608</v>
+        <v>0.2323130103823034</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -768,30 +767,30 @@
         <v>4.353722540108308</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1523513723718964</v>
+        <v>0.2323130103823034</v>
       </c>
       <c r="G9" t="n">
         <v>4.353722540108308</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1523982481882608</v>
+        <v>0.2349400511529411</v>
       </c>
       <c r="I9" t="n">
         <v>2.177308112579369</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1523982481882608</v>
+        <v>0.2364714492235294</v>
       </c>
       <c r="K9" t="n">
         <v>2.177308112579369</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1523079735536756</v>
+        <v>0.2542444889647059</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -805,30 +804,30 @@
         <v>4.353722540108308</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1523735456399593</v>
+        <v>0.2542444889647058</v>
       </c>
       <c r="G10" t="n">
         <v>4.353722540108308</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1540787346380496</v>
+        <v>0.2529265819404869</v>
       </c>
       <c r="I10" t="n">
         <v>2.405150526312388</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1540787346380496</v>
+        <v>0.2528812878702364</v>
       </c>
       <c r="K10" t="n">
         <v>2.405150526312388</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1519434185077895</v>
+        <v>0.2517870210646563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -842,26 +841,26 @@
         <v>4.353722540108308</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1524296565163834</v>
+        <v>0.2517870210646563</v>
       </c>
       <c r="G11" t="n">
         <v>4.353722540108308</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1524638149936007</v>
+        <v>0.2508776150801099</v>
       </c>
       <c r="I11" t="n">
         <v>2.562354885965188</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1524638149936007</v>
+        <v>0.2528812878702365</v>
       </c>
       <c r="K11" t="n">
         <v>2.562354885965188</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
@@ -898,7 +897,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
@@ -935,7 +934,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
@@ -972,7 +971,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
@@ -1009,7 +1008,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
@@ -1043,746 +1042,6 @@
       </c>
       <c r="K16" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.006129481850234507</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>175</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.00611374141169241</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.00617663973350686</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.00617663973350686</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.621760536387246</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.006678152163454651</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>175</v>
-      </c>
-      <c r="E18" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.006661861245507536</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.006262600094901481</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.006262600094901481</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.621760536387246</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.006678152163454651</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>175</v>
-      </c>
-      <c r="E19" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.006661861245507536</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.006543396533113276</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.006536067549209536</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.621760536387246</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.007020010273456359</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>175</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.007018802880358443</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.00712146251322377</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.00711413352932003</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.621760536387246</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.00703667564698258</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>175</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.007018802880358443</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.007195287411255714</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.621760536387246</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.007187958427351978</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.621760536387246</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.5000546059409339</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.5000546059409339</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.02633474236603728</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.02633474236603728</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.5000546059409339</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.5000546059409339</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.04596600748337572</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.04596600748337572</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.5000546059409339</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.5000546059409339</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.06143117628534765</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.06143117628534765</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.5000546059409339</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.5000546059409339</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.0741028698340952</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.0741028698340952</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.5000546059409339</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.5000546059409339</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.08482767349238725</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.08482767349238725</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.05076576841645742</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.05076576841645742</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.1903582751495561</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.08860917105229058</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.08860917105229058</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.1903582751495561</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.1184215446464533</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.1184215446464533</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.1903582751495561</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.1428489057042799</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.1428489057042799</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.1903582751495561</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.963960686151198</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.1635232260094212</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.1635232260094212</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>300</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.1333478949175824</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.1333478949175824</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.007022597964276609</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.007022597964276609</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>300</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.1333478949175824</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.1333478949175824</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.01225760199556686</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.01225760199556686</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>300</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.1333478949175824</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.1333478949175824</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.01638164700942604</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.01638164700942604</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0.05965760287188208</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>300</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.1333478949175824</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.001796848339803497</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.1333478949175824</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.01976076528909205</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.01976076528909205</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0.05965760287188208</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Pfeffikon LU</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>300</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.1333478949175824</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.001796848339803497</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.1333478949175824</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.02262071293130327</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.02262071293130327</v>
       </c>
     </row>
   </sheetData>
